--- a/artfynd/A 29707-2025 artfynd.xlsx
+++ b/artfynd/A 29707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6456176</v>
+        <v>82212510</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>225046</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Fomitopsis pulvinascens</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kanalbanken, Ramnäs, Surahammars kn, Vstm</t>
+          <t>Kanalhagen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566109.0589732173</v>
+        <v>565908</v>
       </c>
       <c r="R2" t="n">
-        <v>6627093.599415125</v>
+        <v>6627160</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-09-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,38 +757,39 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Asplåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82212510</v>
+        <v>82212597</v>
       </c>
       <c r="B3" t="n">
-        <v>89652</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,12 +806,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565908.0834908995</v>
+        <v>565709</v>
       </c>
       <c r="R3" t="n">
-        <v>6627160.047274553</v>
+        <v>6627254</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +857,9 @@
           <t>2020-02-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-02-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +874,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Blandskog, kärr med björk, klibbal</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -914,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82212681</v>
+        <v>338046</v>
       </c>
       <c r="B4" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,37 +908,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kanalhagen, Vstm</t>
+          <t>Kanalbanken, Ramnäs, Surahammars kn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565721.3222750833</v>
+        <v>566318</v>
       </c>
       <c r="R4" t="n">
-        <v>6627164.804292796</v>
+        <v>6627039</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-02-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-02-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,29 +985,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granskog, inslag av asp</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Asp</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1043,12 +1011,7 @@
         <v>82212514</v>
       </c>
       <c r="B5" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565908.0834908995</v>
+        <v>565908</v>
       </c>
       <c r="R5" t="n">
-        <v>6627160.047274553</v>
+        <v>6627160</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,19 +1079,9 @@
           <t>2020-02-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-02-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,6 +1116,545 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>82212681</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kanalhagen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565721</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6627165</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-02-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-02-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granskog, inslag av asp</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4813958</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kanalbanken, Ramnäs, Surahammars kn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566039</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6627135</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2009-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2009-09-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133693936</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långkoxet, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566503</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6626783</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstka plantor</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6456176</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kanalbanken, Ramnäs, Surahammars kn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566109</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6627094</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2009-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2009-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6456177</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kanalbanken, Ramnäs, Surahammars kn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566039</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6627135</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2009-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2009-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
